--- a/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de personas que viven en el hogar</t>
+          <t>Número de personas que viven en el hogar (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,31</t>
+          <t>1,19; 1,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,42</t>
+          <t>1,27; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,38</t>
+          <t>1,18; 1,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,32</t>
+          <t>1,2; 1,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,24</t>
+          <t>1,1; 1,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,29</t>
+          <t>1,14; 1,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,4</t>
+          <t>1,29; 1,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,31</t>
+          <t>1,22; 1,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,33</t>
+          <t>1,23; 1,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,36</t>
+          <t>1,23; 1,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,29</t>
+          <t>1,23; 1,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,35</t>
+          <t>1,28; 1,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,28</t>
+          <t>1,21; 1,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,34</t>
+          <t>1,2; 1,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,39</t>
+          <t>1,29; 1,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,21; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,29</t>
+          <t>1,19; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,41</t>
+          <t>1,26; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,35</t>
+          <t>1,24; 1,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,24</t>
+          <t>1,16; 1,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,35</t>
+          <t>1,26; 1,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,25</t>
+          <t>1,19; 1,25</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,35</t>
+          <t>1,25; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,29</t>
+          <t>1,19; 1,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,35</t>
+          <t>1,24; 1,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,3</t>
+          <t>1,23; 1,31</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,25; 1,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,32</t>
+          <t>1,19; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,36</t>
+          <t>1,19; 1,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,19; 1,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,44</t>
+          <t>1,27; 1,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,31</t>
+          <t>1,13; 1,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,3</t>
+          <t>1,2; 1,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,23</t>
+          <t>1,13; 1,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,31</t>
+          <t>1,18; 1,3</t>
         </is>
       </c>
     </row>
@@ -861,17 +861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,36</t>
+          <t>1,26; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,31</t>
+          <t>1,21; 1,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,28</t>
+          <t>1,18; 1,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,3</t>
+          <t>1,23; 1,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,35</t>
+          <t>1,29; 1,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,21; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,32</t>
+          <t>1,21; 1,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,34</t>
+          <t>1,24; 1,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,25</t>
+          <t>1,15; 1,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,28</t>
+          <t>1,2; 1,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,25</t>
+          <t>1,18; 1,25</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,31</t>
+          <t>1,2; 1,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,34</t>
+          <t>1,24; 1,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,31</t>
+          <t>1,23; 1,3</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,3</t>
+          <t>1,24; 1,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,27</t>
+          <t>1,21; 1,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -653,37 +653,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,33</t>
+          <t>1,19; 1,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,43</t>
+          <t>1,27; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1,1; 1,24</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,12; 1,3</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,31</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,26; 1,42</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>1,13; 1,27</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,37</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 1,43</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 1,23</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,31</t>
+          <t>1,2; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,3</t>
+          <t>1,21; 1,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,4</t>
+          <t>1,28; 1,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,22</t>
+          <t>1,14; 1,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,3</t>
+          <t>1,18; 1,32</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -856,44 +856,44 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1,24; 1,33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1,28; 1,38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,34</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1,21; 1,29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,26; 1,35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,26; 1,36</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1,21; 1,31</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,38</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1,19; 1,28</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,36</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1,23; 1,29</t>
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,28</t>
+          <t>1,22; 1,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,3</t>
+          <t>1,21; 1,29</t>
         </is>
       </c>
     </row>
@@ -928,62 +928,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,32</t>
+          <t>1,27; 1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,4</t>
+          <t>1,23; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,33</t>
+          <t>1,16; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,29</t>
+          <t>1,14; 1,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,42</t>
+          <t>1,21; 1,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,35</t>
+          <t>1,29; 1,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,26</t>
+          <t>1,2; 1,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,24</t>
+          <t>1,19; 1,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,35</t>
+          <t>1,25; 1,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,27</t>
+          <t>1,2; 1,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,25</t>
+          <t>1,18; 1,24</t>
         </is>
       </c>
     </row>
@@ -1068,54 +1068,54 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,29</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,23; 1,3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,23; 1,32</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,21; 1,31</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,24; 1,35</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1,27; 1,36</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,3</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 1,28</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,3</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,32</t>
+          <t>1,25; 1,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,31</t>
+          <t>1,18; 1,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,35</t>
+          <t>1,18; 1,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,3</t>
+          <t>1,22; 1,29</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1276,44 +1276,44 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,29</t>
+          <t>1,25; 1,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1,28; 1,34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 1,25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,28</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 1,3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1,29; 1,35</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,27</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,22; 1,27</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1,21; 1,26</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 1,31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,34</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 1,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1,26; 1,29</t>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,27</t>
+          <t>1,22; 1,26</t>
         </is>
       </c>
     </row>
